--- a/UTCUTS/A1_Inputs/A-I_Classifier_Modes_Demand.xlsx
+++ b/UTCUTS/A1_Inputs/A-I_Classifier_Modes_Demand.xlsx
@@ -2871,5 +2871,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E175BA4F-D0BD-4223-BA98-53102847E318}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80D5E679-80ED-4BBF-9D3C-4F809F3AE855}"/>
 </file>